--- a/data/trans_dic/IP74A6_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP74A6_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que han resulto los pagos de recibos</t>
+          <t>Adulto que han resulto los pagos de recibos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,96; 100,0</t>
+          <t>85,87; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,55; 100,0</t>
+          <t>92,65; 100,0</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,81; 96,09</t>
+          <t>66,31; 96,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,83; 100,0</t>
+          <t>68,5; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,61; 97,03</t>
+          <t>77,68; 97,12</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,24; 88,5</t>
+          <t>55,38; 89,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 95,42</t>
+          <t>70,32; 96,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,2; 90,16</t>
+          <t>70,21; 90,48</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45,75; 93,3</t>
+          <t>39,69; 92,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,58; 87,23</t>
+          <t>32,81; 86,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,78; 83,43</t>
+          <t>47,45; 84,01</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,8; 91,69</t>
+          <t>75,47; 91,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,67; 92,95</t>
+          <t>76,7; 92,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,3; 90,63</t>
+          <t>79,68; 90,33</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que han resulto los pagos de recibos (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12412</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6169; 7184</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11652; 12576</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7212</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13399</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13015</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25573</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9693; 14053</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9487; 13850</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22114; 27650</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13409</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23002</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36412</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9912; 16080</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18702; 25547</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31240; 40255</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7146</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13058</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3204; 7437</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3692; 9775</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9170; 16234</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>49248</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>57738</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>106986</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>43861; 53091</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>50829; 61566</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>99120; 112359</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>